--- a/tests/docs/D3_Test_Cases_Excel.xlsx
+++ b/tests/docs/D3_Test_Cases_Excel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\First\Desktop\student-dormitory-payment-system-Repository-Structure\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\First\Desktop\student-dormitory-payment-system-Repository-Structure\tests\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2142A92-6B73-47B0-B952-17800BD4B137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004BBEF3-AE26-4099-83C2-D67A5F464A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2910" yWindow="525" windowWidth="17205" windowHeight="13560" xr2:uid="{40866869-EFC0-4426-A0C9-8B397FB3E5A5}"/>
+    <workbookView xWindow="20985" yWindow="1095" windowWidth="17205" windowHeight="13560" xr2:uid="{40866869-EFC0-4426-A0C9-8B397FB3E5A5}"/>
   </bookViews>
   <sheets>
     <sheet name="D3_Test_Cases_Excel" sheetId="1" r:id="rId1"/>
@@ -20,77 +20,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="97">
-  <si>
-    <t>???????</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="99">
   <si>
     <t>JR</t>
   </si>
   <si>
-    <t>?????? 1</t>
-  </si>
-  <si>
-    <t>65160381 ????????? ????????</t>
-  </si>
-  <si>
     <t>(Product Owner)</t>
   </si>
   <si>
-    <t>?????? 2</t>
-  </si>
-  <si>
-    <t>65160268 ?????????? ??????</t>
-  </si>
-  <si>
     <t>(Scrum Artifacts / Scrum Master)</t>
   </si>
   <si>
-    <t>?????? 3</t>
-  </si>
-  <si>
-    <t>65160255 ????????????? ????????????</t>
-  </si>
-  <si>
     <t>(Developers)</t>
   </si>
   <si>
-    <t>?????? 4</t>
-  </si>
-  <si>
-    <t>65160132 ???????? ???????</t>
-  </si>
-  <si>
-    <t>?????? 5</t>
-  </si>
-  <si>
-    <t>65160267 ??????????? ????????</t>
-  </si>
-  <si>
     <t>(Quality Assurance / Tester)</t>
   </si>
   <si>
-    <t>?????? 6</t>
-  </si>
-  <si>
-    <t>65160022 ???????? ?????</t>
-  </si>
-  <si>
-    <t>?????????</t>
-  </si>
-  <si>
-    <t>?????</t>
-  </si>
-  <si>
-    <t>????????</t>
-  </si>
-  <si>
-    <t>????????????</t>
-  </si>
-  <si>
-    <t>?????????????????</t>
-  </si>
-  <si>
     <t>TC-001</t>
   </si>
   <si>
@@ -311,6 +257,66 @@
   </si>
   <si>
     <t>201 + readingId</t>
+  </si>
+  <si>
+    <t>Team Name</t>
+  </si>
+  <si>
+    <t>Member 1</t>
+  </si>
+  <si>
+    <t>Member 2</t>
+  </si>
+  <si>
+    <t>Member 3</t>
+  </si>
+  <si>
+    <t>Member 4</t>
+  </si>
+  <si>
+    <t>Member 5</t>
+  </si>
+  <si>
+    <t>Member 6</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Input Data</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>65160381 Parinya Triyakun</t>
+  </si>
+  <si>
+    <t>65160268 Sorrawit Srisuk</t>
+  </si>
+  <si>
+    <t>65160255 Nirattisai Klaysuwan</t>
+  </si>
+  <si>
+    <t>65160132 Aumnat Chakamnan</t>
+  </si>
+  <si>
+    <t>65160267 Weerapat Tapaotong</t>
+  </si>
+  <si>
+    <t>65160022 Phoowadon Teekhao</t>
   </si>
 </sst>
 </file>
@@ -1173,514 +1179,521 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E9DC76-6DE5-40EA-9C13-839C1C5B0CA8}">
   <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" customWidth="1"/>
+    <col min="3" max="3" width="34.5703125" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
         <v>38</v>
       </c>
-      <c r="C24" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" t="s">
-        <v>56</v>
-      </c>
       <c r="F24" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F27" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E28" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F28" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F29" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D32" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E32" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F32" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E34" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E35" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="F35" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E36" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
